--- a/artfynd/A 804-2023 artfynd.xlsx
+++ b/artfynd/A 804-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 804-2023 artfynd.xlsx
+++ b/artfynd/A 804-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -915,6 +915,131 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>125201795</v>
+      </c>
+      <c r="B4" t="n">
+        <v>9398</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>101246</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ekoxe</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lucanus cervus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Säteriet_norr, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>577917</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6398734</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Skadad och kraftigt  angripen av ett tiotal skogsmyror.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 804-2023 artfynd.xlsx
+++ b/artfynd/A 804-2023 artfynd.xlsx
@@ -922,11 +922,6 @@
       <c r="B4" t="n">
         <v>9398</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>LC</t>

--- a/artfynd/A 804-2023 artfynd.xlsx
+++ b/artfynd/A 804-2023 artfynd.xlsx
@@ -782,7 +782,7 @@
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">

--- a/artfynd/A 804-2023 artfynd.xlsx
+++ b/artfynd/A 804-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>96383246</v>
       </c>
       <c r="B2" t="n">
-        <v>84993</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>88953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -700,12 +695,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Clavaria zollingeri</t>
+          <t>Clavaria amethystina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Lév.</t>
+          <t>(Holmsk.) Bull.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -730,10 +725,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578086.4025525784</v>
+        <v>578086</v>
       </c>
       <c r="R2" t="n">
-        <v>6398694.130072508</v>
+        <v>6398694</v>
       </c>
       <c r="S2" t="n">
         <v>36</v>
@@ -763,19 +758,9 @@
           <t>2021-09-29</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-09-29</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -806,12 +791,7 @@
         <v>119300276</v>
       </c>
       <c r="B3" t="n">
-        <v>90522</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91867</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -920,7 +900,7 @@
         <v>125201795</v>
       </c>
       <c r="B4" t="n">
-        <v>9398</v>
+        <v>9406</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
